--- a/reports/2026-02-28.xlsx
+++ b/reports/2026-02-28.xlsx
@@ -16,12 +16,12 @@
     <sheet name="Pullback Setups" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Global Top 20'!$A$1:$K$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reversal Setups'!$A$1:$L$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Breakout Setups'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Breakout Immediate 1-5D'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Breakout Retest 1-5D'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Pullback Setups'!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Global Top 20'!$A$1:$N$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reversal Setups'!$A$1:$U$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Breakout Setups'!$A$1:$U$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Breakout Immediate 1-5D'!$A$1:$U$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Breakout Retest 1-5D'!$A$1:$U$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Pullback Setups'!$A$1:$U$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -554,7 +554,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-02-28 05:01 UTC</t>
+          <t>2026-02-28 18:47 UTC</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -691,6 +691,21 @@
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
+          <t>Global Volume 24h (USD)</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Turnover 24h</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>MEXC Share 24h</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
           <t>Flags</t>
         </is>
       </c>
@@ -701,12 +716,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VIRTUALUSDT</t>
+          <t>ICPUSDT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Virtuals Protocol</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -715,30 +730,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>77.47</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>77.47</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>$0.67</t>
+          <t>$2.39</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>$439.61M</t>
+          <t>$1.30B</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>$1.44M</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>$5.69M</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -746,12 +761,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ICPUSDT</t>
+          <t>DOTUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Internet Computer</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -760,30 +775,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>72.15000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="F3" t="n">
-        <v>72.15000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>$2.45</t>
+          <t>$1.59</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>$1.35B</t>
+          <t>$2.66B</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>$7.62M</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>$13.67M</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -791,44 +806,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LUNCUSDT</t>
+          <t>NEARUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Terra Classic</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>68</v>
+        <v>46.79</v>
       </c>
       <c r="F4" t="n">
-        <v>68</v>
+        <v>46.79</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$1.10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>$236.94M</t>
+          <t>$1.41B</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>$5.68M</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>$5.82M</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -836,12 +851,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DOTUSDT</t>
+          <t>UNIUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -850,30 +865,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>67.8</v>
+        <v>41.3</v>
       </c>
       <c r="F5" t="n">
-        <v>67.8</v>
+        <v>41.3</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$1.55</t>
+          <t>$3.75</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>$2.60B</t>
+          <t>$2.37B</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>$12.85M</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>$7.50M</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -881,12 +896,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PENDLEUSDT</t>
+          <t>AVAXUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pendle</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -895,30 +910,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>67.3</v>
+        <v>40.77</v>
       </c>
       <c r="F6" t="n">
-        <v>67.3</v>
+        <v>40.77</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>$1.25</t>
+          <t>$8.87</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>$206.45M</t>
+          <t>$3.82B</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>$1.07M</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>$15.71M</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -926,44 +941,44 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PIPPINUSDT</t>
+          <t>SUIUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pippin</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>36.38</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>36.38</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>$0.67</t>
+          <t>$0.88</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>$660.89M</t>
+          <t>$3.36B</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>$5.29M</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>$33.45M</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -971,44 +986,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DCRUSDT</t>
+          <t>LTCUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Decred</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>34.72</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>34.72</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>$32.62</t>
+          <t>$53.69</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>$568.43M</t>
+          <t>$4.12B</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>$1.43M</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>$10.23M</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1016,44 +1031,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CCUSDT</t>
+          <t>LINKUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>59.84</v>
+        <v>34.09</v>
       </c>
       <c r="F9" t="n">
-        <v>59.84</v>
+        <v>34.09</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$0.17</t>
+          <t>$8.59</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>$6.38B</t>
+          <t>$6.07B</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>$37.03M</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>$19.84M</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1061,44 +1076,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>STABLEUSDT</t>
+          <t>ADAUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>59.5</v>
+        <v>33.52</v>
       </c>
       <c r="F10" t="n">
-        <v>59.5</v>
+        <v>33.52</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>$0.03</t>
+          <t>$0.27</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>$560.39M</t>
+          <t>$9.80B</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>$2.03M</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>$18.64M</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1106,12 +1121,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ASTERUSDT</t>
+          <t>AAVEUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1120,30 +1135,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>52.6</v>
+        <v>26.87</v>
       </c>
       <c r="F11" t="n">
-        <v>52.6</v>
+        <v>26.87</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>$0.69</t>
+          <t>$109.85</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>$1.72B</t>
+          <t>$1.68B</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>$2.97M</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>$6.59M</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1151,12 +1166,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>POLUSDT</t>
+          <t>HYPEUSDT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Polygon (prev. MATIC)</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1165,30 +1180,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>49.53</v>
+        <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>49.53</v>
+        <v>25.5</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>$0.11</t>
+          <t>$29.28</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>$1.14B</t>
+          <t>$7.61B</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>$1.10M</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>$10.26M</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1196,12 +1211,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ETHFIUSDT</t>
+          <t>PEPEUSDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ether.fi</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1210,30 +1225,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>49</v>
+        <v>25.32</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>25.32</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$0.49</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>$365.28M</t>
+          <t>$1.48B</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>$1.33M</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>$12.47M</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1241,12 +1256,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FILUSDT</t>
+          <t>ZECUSDT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>Zcash</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1255,30 +1270,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>46.88</v>
+        <v>23.78</v>
       </c>
       <c r="F14" t="n">
-        <v>46.88</v>
+        <v>23.78</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>$0.98</t>
+          <t>$212.56</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>$740.72M</t>
+          <t>$3.52B</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>$3.98M</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>$7.97M</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1286,12 +1301,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NEARUSDT</t>
+          <t>BCHUSDT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1300,30 +1315,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>46.79</v>
+        <v>22.89</v>
       </c>
       <c r="F15" t="n">
-        <v>46.79</v>
+        <v>22.89</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>$1.08</t>
+          <t>$448.70</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>$1.40B</t>
+          <t>$8.96B</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>$6.46M</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>$7.98M</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1331,44 +1346,48 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UNIUSDT</t>
+          <t>APTUSDT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Aptos</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>41.3</v>
+        <v>7.17</v>
       </c>
       <c r="F16" t="n">
-        <v>41.3</v>
+        <v>7.17</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>$3.72</t>
+          <t>$0.92</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>$2.36B</t>
+          <t>$717.33M</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>$6.31M</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>$7.42M</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>broken_trend</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1376,227 +1395,51 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AVAXUSDT</t>
+          <t>CHZUSDT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Chiliz</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>40.77</v>
+        <v>2.8</v>
       </c>
       <c r="F17" t="n">
-        <v>40.77</v>
+        <v>2.8</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>$8.89</t>
+          <t>$0.03</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>$3.84B</t>
+          <t>$347.94M</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>$14.20M</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>HBARUSDT</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Hedera</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>reversal</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>40.09</v>
-      </c>
-      <c r="F18" t="n">
-        <v>40.09</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>$0.10</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>$4.29B</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>$3.86M</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>LTCUSDT</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Litecoin</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>reversal</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>34.72</v>
-      </c>
-      <c r="F19" t="n">
-        <v>34.72</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>$54.74</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>$4.21B</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>$8.41M</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>LINKUSDT</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Chainlink</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>reversal</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>34.09</v>
-      </c>
-      <c r="F20" t="n">
-        <v>34.09</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>$8.68</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>$6.15B</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>$11.34M</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ADAUSDT</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Cardano</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>reversal</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="F21" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>$0.28</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>$9.98B</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>$11.95M</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>$5.44M</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>broken_trend</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K21"/>
+  <autoFilter ref="A1:N17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1607,21 +1450,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="25" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1647,40 +1499,85 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Execution Gate Pass</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Spread %</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Bid 0.5% USD</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Ask 0.5% USD</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Bid 1.0% USD</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Ask 1.0% USD</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
           <t>Market Cap</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>24h Volume</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Global Volume 24h (USD)</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Turnover 24h</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>MEXC Share 24h</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Drawdown</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Reclaim</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Flags</t>
         </is>
@@ -1692,45 +1589,48 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VIRTUALUSDT</t>
+          <t>ICPUSDT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Virtuals Protocol</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$0.67</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>$439.61M</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>$1.44M</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>77.47</v>
-      </c>
-      <c r="H2" t="n">
+          <t>$2.39</t>
+        </is>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>$1.30B</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>$5.69M</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>72.15000000000001</v>
+      </c>
+      <c r="Q2" t="n">
         <v>100</v>
       </c>
-      <c r="I2" t="n">
-        <v>82.18000000000001</v>
-      </c>
-      <c r="J2" t="n">
-        <v>59.65</v>
-      </c>
-      <c r="K2" t="n">
-        <v>96.53</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>80.69</v>
+      </c>
+      <c r="S2" t="n">
+        <v>70</v>
+      </c>
+      <c r="T2" t="n">
+        <v>66.48</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1738,45 +1638,48 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ICPUSDT</t>
+          <t>DOTUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Internet Computer</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$2.45</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>$1.35B</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>$7.62M</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>72.15000000000001</v>
-      </c>
-      <c r="H3" t="n">
+          <t>$1.59</t>
+        </is>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>$2.66B</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>$13.67M</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="Q3" t="n">
         <v>100</v>
       </c>
-      <c r="I3" t="n">
-        <v>80.69</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="R3" t="n">
+        <v>65.78</v>
+      </c>
+      <c r="S3" t="n">
         <v>70</v>
       </c>
-      <c r="K3" t="n">
-        <v>66.48</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1784,45 +1687,48 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DOTUSDT</t>
+          <t>NEARUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$1.55</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>$2.60B</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>$12.85M</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="H4" t="n">
+          <t>$1.10</t>
+        </is>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>$1.41B</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>$5.82M</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="Q4" t="n">
         <v>100</v>
       </c>
-      <c r="I4" t="n">
-        <v>65.78</v>
-      </c>
-      <c r="J4" t="n">
-        <v>70</v>
-      </c>
-      <c r="K4" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>78.84999999999999</v>
+      </c>
+      <c r="S4" t="n">
+        <v>57.84</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1830,45 +1736,48 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PENDLEUSDT</t>
+          <t>UNIUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pendle</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$1.25</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>$206.45M</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>$1.07M</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="H5" t="n">
+          <t>$3.75</t>
+        </is>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>$2.37B</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>$7.50M</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="Q5" t="n">
         <v>100</v>
       </c>
-      <c r="I5" t="n">
-        <v>90.23</v>
-      </c>
-      <c r="J5" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="K5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>78.42</v>
+      </c>
+      <c r="S5" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1876,49 +1785,48 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LUNCUSDT</t>
+          <t>AVAXUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Terra Classic</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>$236.94M</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>$5.68M</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>64.77</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>75.09</v>
-      </c>
-      <c r="J6" t="n">
+          <t>$8.87</t>
+        </is>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>$3.82B</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>$15.71M</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>40.77</v>
+      </c>
+      <c r="Q6" t="n">
         <v>100</v>
       </c>
-      <c r="K6" t="n">
-        <v>100</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>overextended</t>
-        </is>
-      </c>
+      <c r="R6" t="n">
+        <v>85.14</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1926,49 +1834,48 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DCRUSDT</t>
+          <t>SUIUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Decred</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$32.62</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>$568.43M</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>$1.43M</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>58.95</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="J7" t="n">
+          <t>$0.88</t>
+        </is>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>$3.36B</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>$33.45M</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>36.38</v>
+      </c>
+      <c r="Q7" t="n">
         <v>100</v>
       </c>
-      <c r="K7" t="n">
-        <v>100</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>overextended</t>
-        </is>
-      </c>
+      <c r="R7" t="n">
+        <v>87.31</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>33.96</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1976,45 +1883,48 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ASTERUSDT</t>
+          <t>LTCUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$0.69</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>$1.72B</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>$2.97M</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="H8" t="n">
-        <v>95.89</v>
-      </c>
-      <c r="I8" t="n">
-        <v>95.34</v>
-      </c>
-      <c r="J8" t="n">
-        <v>60</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>$53.69</t>
+        </is>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>$4.12B</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>$10.23M</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>100</v>
+      </c>
+      <c r="R8" t="n">
+        <v>89.06999999999999</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2022,45 +1932,48 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>POLUSDT</t>
+          <t>LINKUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Polygon (prev. MATIC)</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$0.11</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>$1.14B</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>$1.10M</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>49.53</v>
-      </c>
-      <c r="H9" t="n">
-        <v>67.56</v>
-      </c>
-      <c r="I9" t="n">
-        <v>91.38</v>
-      </c>
-      <c r="J9" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>$8.59</t>
+        </is>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>$6.07B</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>$19.84M</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>34.09</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+      <c r="R9" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2068,45 +1981,48 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ETHFIUSDT</t>
+          <t>ADAUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ether.fi</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$0.49</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>$365.28M</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>$1.33M</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>49</v>
-      </c>
-      <c r="H10" t="n">
+          <t>$0.27</t>
+        </is>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>$9.80B</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>$18.64M</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="Q10" t="n">
         <v>100</v>
       </c>
-      <c r="I10" t="n">
-        <v>83.68000000000001</v>
-      </c>
-      <c r="J10" t="n">
-        <v>59.74</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>85.06999999999999</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2114,48 +2030,51 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FILUSDT</t>
+          <t>AAVEUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$0.98</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>$740.72M</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>$3.98M</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>46.88</v>
-      </c>
-      <c r="H11" t="n">
+          <t>$109.85</t>
+        </is>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>$1.68B</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>$6.59M</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>26.87</v>
+      </c>
+      <c r="Q11" t="n">
         <v>100</v>
       </c>
-      <c r="I11" t="n">
-        <v>79.16</v>
-      </c>
-      <c r="J11" t="n">
-        <v>57.82</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>89.56999999999999</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L11"/>
+  <autoFilter ref="A1:U11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2166,21 +2085,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="25" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2206,47 +2134,92 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Execution Gate Pass</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Spread %</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Bid 0.5% USD</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Ask 0.5% USD</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Bid 1.0% USD</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Ask 1.0% USD</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
           <t>Market Cap</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>24h Volume</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Global Volume 24h (USD)</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Turnover 24h</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>MEXC Share 24h</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Breakout</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Momentum</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Flags</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:U1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2257,21 +2230,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="25" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2297,47 +2279,92 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Execution Gate Pass</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Spread %</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Bid 0.5% USD</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Ask 0.5% USD</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Bid 1.0% USD</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Ask 1.0% USD</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
           <t>Market Cap</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>24h Volume</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Global Volume 24h (USD)</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Turnover 24h</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>MEXC Share 24h</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Breakout</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Momentum</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Flags</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:U1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2348,21 +2375,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="25" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2388,47 +2424,92 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Execution Gate Pass</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Spread %</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Bid 0.5% USD</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Ask 0.5% USD</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Bid 1.0% USD</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Ask 1.0% USD</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
           <t>Market Cap</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>24h Volume</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Global Volume 24h (USD)</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Turnover 24h</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>MEXC Share 24h</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Breakout</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Momentum</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Flags</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:U1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2439,21 +2520,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="25" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2479,40 +2569,85 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Execution Gate Pass</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Spread %</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Bid 0.5% USD</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Ask 0.5% USD</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Bid 1.0% USD</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Depth Ask 1.0% USD</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
           <t>Market Cap</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>24h Volume</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Global Volume 24h (USD)</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Turnover 24h</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>MEXC Share 24h</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Pullback</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Rebound</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Flags</t>
         </is>
@@ -2524,45 +2659,52 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LUNCUSDT</t>
+          <t>NEARUSDT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Terra Classic</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>$236.94M</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>$5.68M</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>68</v>
-      </c>
-      <c r="H2" t="n">
+          <t>$1.10</t>
+        </is>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>$1.41B</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>$5.82M</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
         <v>100</v>
       </c>
-      <c r="I2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J2" t="n">
-        <v>100</v>
-      </c>
-      <c r="K2" t="n">
-        <v>100</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>broken_trend</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2570,45 +2712,52 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PIPPINUSDT</t>
+          <t>ADAUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pippin</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$0.67</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>$660.89M</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>$5.29M</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>60</v>
-      </c>
-      <c r="H3" t="n">
+          <t>$0.27</t>
+        </is>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>$9.80B</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>$18.64M</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
         <v>100</v>
       </c>
-      <c r="I3" t="n">
-        <v>20</v>
-      </c>
-      <c r="J3" t="n">
-        <v>60</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>24</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>broken_trend</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2616,45 +2765,52 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DCRUSDT</t>
+          <t>LTCUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Decred</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$32.62</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>$568.43M</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>$1.43M</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>60</v>
-      </c>
-      <c r="H4" t="n">
+          <t>$53.69</t>
+        </is>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>$4.12B</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>$10.23M</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
         <v>100</v>
       </c>
-      <c r="I4" t="n">
-        <v>20</v>
-      </c>
-      <c r="J4" t="n">
-        <v>60</v>
-      </c>
-      <c r="K4" t="n">
-        <v>100</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>24</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>broken_trend</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2662,45 +2818,52 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CCUSDT</t>
+          <t>DOTUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$0.17</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>$6.38B</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>$37.03M</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>59.84</v>
-      </c>
-      <c r="H5" t="n">
-        <v>90</v>
-      </c>
-      <c r="I5" t="n">
-        <v>40</v>
-      </c>
-      <c r="J5" t="n">
-        <v>39.21</v>
-      </c>
-      <c r="K5" t="n">
+          <t>$1.59</t>
+        </is>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>$2.66B</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>$13.67M</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>80</v>
+      </c>
+      <c r="S5" t="n">
+        <v>60</v>
+      </c>
+      <c r="T5" t="n">
         <v>100</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>broken_trend</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2708,45 +2871,52 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>STABLEUSDT</t>
+          <t>ICPUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$0.03</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>$560.39M</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>$2.03M</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>100</v>
-      </c>
-      <c r="I6" t="n">
-        <v>20</v>
-      </c>
-      <c r="J6" t="n">
-        <v>57.51</v>
-      </c>
-      <c r="K6" t="n">
-        <v>55.96</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>$2.39</t>
+        </is>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>$1.30B</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>$5.69M</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>10</v>
+      </c>
+      <c r="S6" t="n">
+        <v>60</v>
+      </c>
+      <c r="T6" t="n">
+        <v>80</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>broken_trend</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2754,45 +2924,52 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ASTERUSDT</t>
+          <t>UNIUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$0.69</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>$1.72B</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>$2.97M</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>20</v>
-      </c>
-      <c r="I7" t="n">
-        <v>100</v>
-      </c>
-      <c r="J7" t="n">
-        <v>16</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>$3.75</t>
+        </is>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>$2.37B</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>$7.50M</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>10</v>
+      </c>
+      <c r="S7" t="n">
+        <v>54.44</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>broken_trend</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2800,45 +2977,48 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEARUSDT</t>
+          <t>APTUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Aptos</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$1.08</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>$1.40B</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>$6.46M</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>24.78</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>100</v>
-      </c>
-      <c r="J8" t="n">
-        <v>47.84</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6.89</v>
+          <t>$0.92</t>
+        </is>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>$717.33M</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
+        <is>
+          <t>$7.42M</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>10</v>
+      </c>
+      <c r="S8" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="T8" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>broken_trend</t>
         </is>
@@ -2850,45 +3030,48 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FILUSDT</t>
+          <t>HYPEUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$0.98</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>$740.72M</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>$3.98M</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>24.78</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>100</v>
-      </c>
-      <c r="J9" t="n">
-        <v>47.82</v>
-      </c>
-      <c r="K9" t="n">
-        <v>7.39</v>
+          <t>$29.28</t>
+        </is>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>$7.61B</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
+        <is>
+          <t>$10.26M</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" t="n">
+        <v>32</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>broken_trend</t>
         </is>
@@ -2900,45 +3083,48 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DOTUSDT</t>
+          <t>SUIUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$1.55</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>$2.60B</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>$12.85M</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
+          <t>$0.88</t>
+        </is>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>$3.36B</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>$33.45M</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S10" t="n">
+        <v>24</v>
+      </c>
+      <c r="T10" t="n">
         <v>80</v>
       </c>
-      <c r="J10" t="n">
-        <v>68</v>
-      </c>
-      <c r="K10" t="n">
-        <v>100</v>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>broken_trend</t>
         </is>
@@ -2950,52 +3136,55 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HBARUSDT</t>
+          <t>LINKUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hedera</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$0.10</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>$4.29B</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>$3.86M</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>22.53</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>100</v>
-      </c>
-      <c r="J11" t="n">
-        <v>25.28</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+          <t>$8.59</t>
+        </is>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>$6.07B</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>$19.84M</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S11" t="n">
+        <v>24</v>
+      </c>
+      <c r="T11" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>broken_trend</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L11"/>
+  <autoFilter ref="A1:U11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>